--- a/Vlad/export/Приложение_В.xlsx
+++ b/Vlad/export/Приложение_В.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,88 +614,88 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>38.343</v>
+        <v>47.355</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>59.174</v>
+        <v>61.445</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20.831</v>
+        <v>14.089</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37.227</v>
+        <v>46.522</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>59.44</v>
+        <v>60.751</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.213</v>
+        <v>14.23</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1737</v>
+        <v>-0.9519</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-1.9225</v>
+        <v>-3.3695</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28.772</v>
+        <v>23.682</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>32.722</v>
+        <v>27.38</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.114000000000001</v>
+        <v>8.641</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8.586</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>52.902</v>
+        <v>58.244</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>51.665</v>
+        <v>56.842</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>200.5661</v>
+        <v>145.2173</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>179.278</v>
+        <v>133.8172</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>125.3538</v>
+        <v>90.7608</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>125.3538</v>
+        <v>90.7608</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>117.2083</v>
+        <v>146.5717</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>101.8298</v>
+        <v>139.1615</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>1.0695</v>
+        <v>0.6192</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1.231</v>
+        <v>0.6522</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>77.765</v>
+        <v>66.761</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>75.836</v>
+        <v>65.85899999999999</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>15.553</v>
+        <v>13.352</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>15.167</v>
+        <v>13.172</v>
       </c>
     </row>
     <row r="3">
@@ -703,88 +703,88 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>36.403</v>
+        <v>44.184</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>57.53</v>
+        <v>60.546</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21.126</v>
+        <v>16.362</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>35.217</v>
+        <v>43.249</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>58.121</v>
+        <v>60.332</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>22.904</v>
+        <v>17.082</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.5047</v>
+        <v>-0.6907</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-1.6967</v>
+        <v>-2.9583</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28.211</v>
+        <v>25.822</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>33.046</v>
+        <v>29.479</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>7.59</v>
+        <v>8.769</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8.445</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>51.014</v>
+        <v>56.405</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>50.043</v>
+        <v>55.031</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>157.99</v>
+        <v>122.417</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>141.4294</v>
+        <v>111.3098</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>100.1888</v>
+        <v>77.7251</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>100.1888</v>
+        <v>77.7251</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>83.36060000000001</v>
+        <v>107.3991</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>75.8245</v>
+        <v>95.1738</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.2019</v>
+        <v>0.7237</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>1.3213</v>
+        <v>0.8167</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>59.459</v>
+        <v>54.172</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>57.777</v>
+        <v>53.255</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>11.892</v>
+        <v>10.834</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>11.555</v>
+        <v>10.651</v>
       </c>
     </row>
     <row r="4">
@@ -792,88 +792,88 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>34.931</v>
+        <v>41.827</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>56.424</v>
+        <v>59.865</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>21.493</v>
+        <v>18.038</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33.683</v>
+        <v>40.807</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>57.166</v>
+        <v>59.818</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23.483</v>
+        <v>19.012</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7494</v>
+        <v>-0.4742</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-1.5223</v>
+        <v>-2.7883</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.056</v>
+        <v>27.322</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>33.371</v>
+        <v>31.535</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.313</v>
+        <v>8.81</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8.366</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>49.708</v>
+        <v>55.014</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>48.846</v>
+        <v>53.786</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>124.8688</v>
+        <v>100.2025</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>112.6559</v>
+        <v>91.07859999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>80.36109999999999</v>
+        <v>64.6468</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>80.36109999999999</v>
+        <v>64.6468</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>61.8273</v>
+        <v>79.7812</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>57.7681</v>
+        <v>73.0742</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.2998</v>
+        <v>0.8103</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>1.3911</v>
+        <v>0.8847</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>46.014</v>
+        <v>43.112</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>44.568</v>
+        <v>42.247</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>9.202999999999999</v>
+        <v>8.622</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>8.914</v>
+        <v>8.449</v>
       </c>
     </row>
     <row r="5">
@@ -881,88 +881,88 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>34.103</v>
+        <v>40.177</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>54.763</v>
+        <v>58.621</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20.659</v>
+        <v>18.443</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32.787</v>
+        <v>39.074</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55.639</v>
+        <v>58.703</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>22.852</v>
+        <v>19.629</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6669</v>
+        <v>-0.2831</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-1.356</v>
+        <v>-2.5193</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.274</v>
+        <v>27.175</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>32.167</v>
+        <v>31.36</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.281</v>
+        <v>8.448</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7.959</v>
+        <v>9.211</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>48.407</v>
+        <v>53.482</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>47.514</v>
+        <v>52.234</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>100.443</v>
+        <v>81.9547</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>91.68980000000001</v>
+        <v>75.01690000000001</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>65.616</v>
+        <v>53.7408</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>65.616</v>
+        <v>53.7408</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>51.7977</v>
+        <v>60.6034</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>45.0169</v>
+        <v>54.1578</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1.2668</v>
+        <v>0.8868</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>1.4576</v>
+        <v>0.9923</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>36.79</v>
+        <v>34.671</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>35.532</v>
+        <v>33.874</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>7.358</v>
+        <v>6.934</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>7.106</v>
+        <v>6.775</v>
       </c>
     </row>
     <row r="6">
@@ -970,88 +970,88 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>33.384</v>
+        <v>38.702</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>53.409</v>
+        <v>57.477</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20.025</v>
+        <v>18.774</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.999</v>
+        <v>37.516</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.409</v>
+        <v>57.676</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22.409</v>
+        <v>20.16</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7040999999999999</v>
+        <v>-0.0915</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-1.1615</v>
+        <v>-2.2782</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26.388</v>
+        <v>26.974</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>31.14</v>
+        <v>31.268</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.067</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7.569</v>
+        <v>8.83</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>47.282</v>
+        <v>52.098</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46.408</v>
+        <v>50.871</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>82.9366</v>
+        <v>68.0791</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>76.4023</v>
+        <v>62.7281</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>55.0089</v>
+        <v>45.3861</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>55.0089</v>
+        <v>45.3861</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>42.9209</v>
+        <v>47.1097</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>35.8275</v>
+        <v>41.6882</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.2816</v>
+        <v>0.9634</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1.5354</v>
+        <v>1.0887</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>30.269</v>
+        <v>28.379</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>29.15</v>
+        <v>27.639</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>6.054</v>
+        <v>5.676</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>5.83</v>
+        <v>5.528</v>
       </c>
     </row>
     <row r="7">
@@ -1059,88 +1059,88 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>32.741</v>
+        <v>37.349</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>52.266</v>
+        <v>56.403</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>19.525</v>
+        <v>19.053</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>31.287</v>
+        <v>36.079</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.383</v>
+        <v>56.714</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>22.096</v>
+        <v>20.635</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8087</v>
+        <v>0.0977</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-1.054</v>
+        <v>-2.0573</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.483</v>
+        <v>26.757</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>30.515</v>
+        <v>31.229</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.766</v>
+        <v>7.801</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7.365</v>
+        <v>8.537000000000001</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46.291</v>
+        <v>50.825</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>45.49</v>
+        <v>49.636</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>69.86799999999999</v>
+        <v>57.3771</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>64.8403</v>
+        <v>53.1907</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>47.0614</v>
+        <v>38.8997</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>47.0614</v>
+        <v>38.8997</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>35.559</v>
+        <v>37.4364</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>29.8157</v>
+        <v>33.0479</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.3235</v>
+        <v>1.0391</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>1.5784</v>
+        <v>1.1771</v>
       </c>
       <c r="X7" s="2" t="n">
         <v>65</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>25.453</v>
+        <v>23.599</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>24.44</v>
+        <v>22.908</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>5.091</v>
+        <v>4.72</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>4.888</v>
+        <v>4.582</v>
       </c>
     </row>
     <row r="8">
@@ -1148,88 +1148,88 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>32.154</v>
+        <v>36.086</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>51.271</v>
+        <v>55.374</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.117</v>
+        <v>19.288</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30.63</v>
+        <v>34.732</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52.502</v>
+        <v>55.798</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21.872</v>
+        <v>21.066</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8666</v>
+        <v>0.2845</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0.9101</v>
+        <v>-1.8499</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24.829</v>
+        <v>26.524</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>29.915</v>
+        <v>31.214</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.578</v>
+        <v>7.521</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7.134</v>
+        <v>8.298</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>45.435</v>
+        <v>49.633</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>44.678</v>
+        <v>48.489</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>59.8125</v>
+        <v>49.0043</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>55.8507</v>
+        <v>45.6852</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>40.9243</v>
+        <v>33.7961</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>40.9243</v>
+        <v>33.7961</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>30.3901</v>
+        <v>30.3433</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>25.0158</v>
+        <v>26.8216</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.3466</v>
+        <v>1.1138</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1.6359</v>
+        <v>1.26</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>21.78</v>
+        <v>19.906</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>20.851</v>
+        <v>19.255</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>4.356</v>
+        <v>3.981</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>4.17</v>
+        <v>3.851</v>
       </c>
     </row>
     <row r="9">
@@ -1237,88 +1237,88 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>31.61</v>
+        <v>34.892</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>50.384</v>
+        <v>54.371</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>18.774</v>
+        <v>19.479</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>30.016</v>
+        <v>33.453</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>51.728</v>
+        <v>54.91</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>21.712</v>
+        <v>21.458</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8966</v>
+        <v>0.4102</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-1.5309</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.333</v>
+        <v>26.456</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>29.348</v>
+        <v>30.85</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.455</v>
+        <v>7.387</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.894</v>
+        <v>7.861</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>44.673</v>
+        <v>48.53</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>43.947</v>
+        <v>47.347</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>51.8888</v>
+        <v>42.3661</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>48.7057</v>
+        <v>39.7028</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>36.0724</v>
+        <v>29.7306</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>36.0724</v>
+        <v>29.7306</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>26.5506</v>
+        <v>25.5404</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>21.1814</v>
+        <v>21.4253</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.3586</v>
+        <v>1.1641</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>1.703</v>
+        <v>1.3876</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>18.907</v>
+        <v>17.007</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>18.045</v>
+        <v>16.389</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>3.781</v>
+        <v>3.401</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>3.609</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="10">
@@ -1326,88 +1326,88 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>31.099</v>
+        <v>33.753</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>49.576</v>
+        <v>53.379</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>18.477</v>
+        <v>19.627</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>29.434</v>
+        <v>32.227</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>51.033</v>
+        <v>54.038</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>21.598</v>
+        <v>21.81</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0.5579</v>
+        <v>-1.2428</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.762</v>
+        <v>25.981</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>28.812</v>
+        <v>30.586</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.263</v>
+        <v>7.011</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6.656</v>
+        <v>7.533</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>43.958</v>
+        <v>47.4</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>43.282</v>
+        <v>46.278</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45.5225</v>
+        <v>37.0394</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>42.9233</v>
+        <v>34.879</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>32.1627</v>
+        <v>26.4567</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>32.1627</v>
+        <v>26.4567</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>23.123</v>
+        <v>20.952</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>18.1011</v>
+        <v>17.604</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1.3909</v>
+        <v>1.2627</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.7768</v>
+        <v>1.5029</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>16.613</v>
+        <v>14.7</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>15.806</v>
+        <v>14.109</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>3.323</v>
+        <v>2.94</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>3.161</v>
+        <v>2.822</v>
       </c>
     </row>
     <row r="11">
@@ -1415,88 +1415,88 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>30.615</v>
+        <v>32.758</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>48.828</v>
+        <v>52.887</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18.212</v>
+        <v>20.129</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>28.879</v>
+        <v>31.143</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>50.398</v>
+        <v>53.458</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>21.519</v>
+        <v>22.315</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.0341</v>
+        <v>0.8468</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0.421</v>
+        <v>-0.9566</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23.299</v>
+        <v>26.161</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>28.437</v>
+        <v>30.554</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.121</v>
+        <v>6.879</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6.497</v>
+        <v>7.282</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>43.299</v>
+        <v>46.685</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>42.676</v>
+        <v>45.463</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>40.324</v>
+        <v>32.7186</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>38.1719</v>
+        <v>31.1513</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>28.962</v>
+        <v>23.7953</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>28.962</v>
+        <v>23.7953</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>20.4877</v>
+        <v>17.7749</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>15.8122</v>
+        <v>14.7126</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.4136</v>
+        <v>1.3387</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>1.8316</v>
+        <v>1.6173</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>14.749</v>
+        <v>12.875</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>13.988</v>
+        <v>12.306</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>2.95</v>
+        <v>2.575</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>2.798</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="12">
@@ -1504,88 +1504,88 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>30.153</v>
+        <v>31.583</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>48.125</v>
+        <v>52.099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>17.972</v>
+        <v>20.516</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.345</v>
+        <v>29.87</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>49.81</v>
+        <v>52.842</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21.464</v>
+        <v>22.972</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.1296</v>
+        <v>1.0777</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0.2076</v>
+        <v>-0.4267</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22.771</v>
+        <v>26.114</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>27.934</v>
+        <v>30.192</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.929</v>
+        <v>6.676</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6.262</v>
+        <v>6.793</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>42.669</v>
+        <v>45.718</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>42.105</v>
+        <v>44.539</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>36.0199</v>
+        <v>29.584</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>34.2169</v>
+        <v>28.2518</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>26.3067</v>
+        <v>21.9141</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>26.3067</v>
+        <v>21.9141</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>18.1194</v>
+        <v>15.3131</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>13.7232</v>
+        <v>11.9793</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1.4518</v>
+        <v>1.4311</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>1.9169</v>
+        <v>1.8293</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>13.214</v>
+        <v>11.477</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>12.49</v>
+        <v>10.914</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>2.643</v>
+        <v>2.295</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>2.498</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="13">
@@ -1593,88 +1593,88 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>29.8</v>
+        <v>30.088</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>47.906</v>
+        <v>48.625</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>18.106</v>
+        <v>18.537</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>27.915</v>
+        <v>29.709</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>49.505</v>
+        <v>53.128</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>21.589</v>
+        <v>23.42</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.2053</v>
+        <v>1.0326</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.1324</v>
+        <v>-0.2152</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22.779</v>
+        <v>23.754</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>27.405</v>
+        <v>30.284</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.879</v>
+        <v>6.25</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5.948</v>
+        <v>6.649</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>42.395</v>
+        <v>42.998</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>41.75</v>
+        <v>44.635</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>32.4139</v>
+        <v>26.9196</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>31.0175</v>
+        <v>25.8709</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>24.0789</v>
+        <v>20.3167</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>24.0789</v>
+        <v>20.3167</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>16.2463</v>
+        <v>14.3778</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>11.7288</v>
+        <v>10.6152</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.4821</v>
+        <v>1.4131</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>2.053</v>
+        <v>1.9139</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>11.967</v>
+        <v>10.185</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>11.273</v>
+        <v>10.069</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>2.393</v>
+        <v>2.037</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>2.255</v>
+        <v>2.014</v>
       </c>
     </row>
     <row r="14">
@@ -1682,177 +1682,88 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>28.878</v>
+        <v>28.342</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>44.96</v>
+        <v>44.367</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16.081</v>
+        <v>16.025</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28.335</v>
+        <v>29.999</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>50.186</v>
+        <v>53.244</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>21.85</v>
+        <v>23.245</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.0046</v>
+        <v>1.0216</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.1136</v>
+        <v>-2.4967</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20.663</v>
+        <v>20.572</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>27.743</v>
+        <v>36.949</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.586</v>
+        <v>5.568</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6.006</v>
+        <v>11.207</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>40.214</v>
+        <v>39.65</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>42.32</v>
+        <v>45.977</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>29.6212</v>
+        <v>24.8222</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>28.5158</v>
+        <v>24.3189</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>22.3881</v>
+        <v>19.094</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>22.3881</v>
+        <v>19.094</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>15.9707</v>
+        <v>13.555</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>10.9454</v>
+        <v>19.0687</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1.4018</v>
+        <v>1.4086</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>2.0454</v>
+        <v>1.0013</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>10.812</v>
+        <v>9.065</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>10.626</v>
+        <v>9.547000000000001</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>2.162</v>
+        <v>1.813</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>2.125</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>27.66</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>41.335</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>13.675</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>29.211</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>49.825</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20.614</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0.8104</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-2.4562</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>17.978</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>33.322</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>5.114</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>10.252</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>37.46</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>43.416</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>27.4105</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>27.2199</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>21.085</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>21.085</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>15.923</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>20.7221</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>1.3242</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>1.0175</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="Y15" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="Z15" s="2" t="n">
-        <v>9.788</v>
-      </c>
-      <c r="AA15" s="2" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="AB15" s="2" t="n">
-        <v>1.958</v>
-      </c>
-      <c r="AC15" s="2" t="n">
-        <v>2.058</v>
+        <v>1.909</v>
       </c>
     </row>
   </sheetData>
